--- a/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
+++ b/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
@@ -29170,7 +29170,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -39093,7 +39093,7 @@
       </c>
       <c r="F585" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G585" s="3" t="inlineStr">
@@ -42787,7 +42787,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -42802,7 +42802,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -44239,7 +44239,7 @@
           <t>A5 | 545呎 (2房)
 $2070万
 $37,978/呎
-(26年-08月-21日)</t>
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr"/>
@@ -45643,12 +45643,12 @@
 (25年-12月-18日)</t>
         </is>
       </c>
-      <c r="D41" s="24" t="inlineStr">
+      <c r="D41" s="22" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">

--- a/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
+++ b/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
@@ -7665,38 +7665,30 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I107" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>14485500</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>30053</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K107" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L107" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K107" s="5" t="n">
+        <v>14485500</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>30053</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
@@ -7705,7 +7697,7 @@
       </c>
       <c r="N107" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -11959,38 +11951,30 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H172" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I172" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="n">
+        <v>37022000</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>40773</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K172" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L172" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K172" s="5" t="n">
+        <v>37022000</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>40773</v>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
@@ -11999,7 +11983,7 @@
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -25856,7 +25840,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -26516,7 +26500,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -33278,7 +33262,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H495" s="5" t="n">
@@ -36972,7 +36956,7 @@
       </c>
       <c r="G552" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H552" s="5" t="n">
@@ -39299,12 +39283,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>142</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -40715,12 +40699,12 @@
 (25年-12月-23日)</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="I24" s="23" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1449万
+$30,053/呎
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
@@ -41239,12 +41223,12 @@
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr"/>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$3702万
+$40,773/呎
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -43773,7 +43757,7 @@
           <t>B1 | 478呎 (2房)
 $1430万
 $29,914/呎
-(26年-08月-18日)</t>
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="I21" s="25" t="inlineStr">
@@ -43868,7 +43852,7 @@
           <t>B1 | 478呎 (2房)
 $1420万
 $29,697/呎
-(26年-08月-14日)</t>
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="I22" s="25" t="inlineStr">
@@ -44793,7 +44777,7 @@
           <t>A2 | 446呎 (2房)
 $1580万
 $35,426/呎
-(26年-08月-25日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -45388,7 +45372,7 @@
           <t>B1 | 478呎 (2房)
 $1209万
 $25,295/呎
-(26年-08月-06日)</t>
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="I38" s="23" t="inlineStr">

--- a/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
+++ b/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
@@ -12525,7 +12525,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -12535,12 +12535,12 @@
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J181" s="3" t="inlineStr">
@@ -12550,12 +12550,12 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L181" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M181" s="3" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="N181" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15701,7 +15701,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -15711,12 +15711,12 @@
       </c>
       <c r="H229" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I229" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J229" s="3" t="inlineStr">
@@ -15726,12 +15726,12 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L229" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M229" s="3" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="N229" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19661,7 +19661,7 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -19671,12 +19671,12 @@
       </c>
       <c r="H289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J289" s="3" t="inlineStr">
@@ -19686,12 +19686,12 @@
       </c>
       <c r="K289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M289" s="3" t="inlineStr">
@@ -19701,7 +19701,7 @@
       </c>
       <c r="N289" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -39273,7 +39273,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39293,7 +39293,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>125</t>
         </is>
       </c>
     </row>
@@ -41360,12 +41360,12 @@
 (25年-12月-16日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="24" t="inlineStr">
         <is>
           <t>A5 | 612呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr"/>
@@ -41812,12 +41812,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="F34" s="24" t="inlineStr">
         <is>
           <t>A5 | 612呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr"/>
@@ -42377,12 +42377,12 @@
 (25年-12月-16日)</t>
         </is>
       </c>
-      <c r="F39" s="21" t="inlineStr">
+      <c r="F39" s="24" t="inlineStr">
         <is>
           <t>A5 | 612呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr"/>

--- a/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
+++ b/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
@@ -17508,7 +17508,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -18238,7 +18238,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -21445,7 +21445,7 @@
       </c>
       <c r="F317" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -31282,7 +31282,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -32462,7 +32462,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H483" s="5" t="n">
@@ -35205,38 +35205,30 @@
       </c>
       <c r="F525" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G525" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H525" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I525" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H525" s="5" t="n">
+        <v>15523900</v>
+      </c>
+      <c r="I525" s="5" t="n">
+        <v>34807</v>
       </c>
       <c r="J525" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K525" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L525" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K525" s="5" t="n">
+        <v>15523900</v>
+      </c>
+      <c r="L525" s="5" t="n">
+        <v>34807</v>
       </c>
       <c r="M525" s="3" t="inlineStr">
         <is>
@@ -35245,7 +35237,7 @@
       </c>
       <c r="N525" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -42019,7 +42011,7 @@
           <t>A1 | 908呎 (4+房)
 $3668万
 $40,396/呎
-(26年-08月-10日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="D36" s="24" t="inlineStr">
@@ -42140,7 +42132,7 @@
           <t>A2 | 450呎 (2房)
 $1544万
 $34,318/呎
-(26年-08月-25日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="E37" s="25" t="inlineStr">
@@ -42771,7 +42763,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -42781,12 +42773,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -42920,12 +42912,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="Q5" s="22" t="inlineStr">
+      <c r="Q5" s="24" t="inlineStr">
         <is>
           <t>PSH B | 3553呎 (4+房)
 招标单位
 -
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="R5" s="20" t="inlineStr"/>
@@ -44492,7 +44484,7 @@
           <t>A2 | 446呎 (2房)
 $1649万
 $36,981/呎
-(26年-08月-31日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -44698,7 +44690,7 @@
           <t>A5 | 545呎 (2房)
 $2044万
 $37,501/呎
-(26年-08月-31日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr"/>
@@ -45057,12 +45049,12 @@
 (25年-12月-12日)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1552万
+$34,807/呎
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">

--- a/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
+++ b/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
@@ -6415,7 +6415,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -19661,7 +19661,7 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -32400,7 +32400,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H482" s="5" t="n">
@@ -39265,7 +39265,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39280,7 +39280,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -40424,12 +40424,12 @@
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr"/>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -42369,12 +42369,12 @@
 (25年-12月-16日)</t>
         </is>
       </c>
-      <c r="F39" s="24" t="inlineStr">
+      <c r="F39" s="22" t="inlineStr">
         <is>
           <t>A5 | 612呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr"/>
@@ -43835,7 +43835,7 @@
           <t>A5 | 545呎 (2房)
 $2116万
 $38,826/呎
-(26年-08月-25日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr"/>
@@ -44699,7 +44699,7 @@
           <t>B1 | 478呎 (2房)
 $1362万
 $28,502/呎
-(26年-08月-25日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">

--- a/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
+++ b/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
@@ -7670,7 +7670,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J121" s="3" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L121" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M121" s="3" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="N121" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12525,7 +12525,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -22805,7 +22805,7 @@
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
@@ -26107,7 +26107,7 @@
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
@@ -26117,12 +26117,12 @@
       </c>
       <c r="H386" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I386" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J386" s="3" t="inlineStr">
@@ -26132,12 +26132,12 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M386" s="3" t="inlineStr">
@@ -26147,7 +26147,7 @@
       </c>
       <c r="N386" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -39069,38 +39069,30 @@
       </c>
       <c r="F585" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G585" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H585" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I585" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H585" s="5" t="n">
+        <v>14458000</v>
+      </c>
+      <c r="I585" s="5" t="n">
+        <v>32417</v>
       </c>
       <c r="J585" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K585" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L585" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K585" s="5" t="n">
+        <v>14458000</v>
+      </c>
+      <c r="L585" s="5" t="n">
+        <v>32417</v>
       </c>
       <c r="M585" s="3" t="inlineStr">
         <is>
@@ -39109,7 +39101,7 @@
       </c>
       <c r="N585" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39280,12 +39272,12 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>124</t>
         </is>
       </c>
     </row>
@@ -40696,7 +40688,7 @@
           <t>B10 | 482呎 (2房)
 $1449万
 $30,053/呎
-(26年-09月-08日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
@@ -40787,12 +40779,12 @@
 (25年-12月-03日)</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="24" t="inlineStr">
         <is>
           <t>A5 | 612呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr"/>
@@ -41352,12 +41344,12 @@
 (25年-12月-16日)</t>
         </is>
       </c>
-      <c r="F30" s="24" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>A5 | 612呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr"/>
@@ -42773,12 +42765,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -43214,12 +43206,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="O11" s="24" t="inlineStr">
+      <c r="O11" s="22" t="inlineStr">
         <is>
           <t>D | 1365呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="P11" s="20" t="inlineStr"/>
@@ -43711,12 +43703,12 @@
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr"/>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -45619,12 +45611,12 @@
 (25年-12月-18日)</t>
         </is>
       </c>
-      <c r="D41" s="22" t="inlineStr">
+      <c r="D41" s="23" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1446万
+$32,417/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">

--- a/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
+++ b/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
@@ -33901,7 +33901,7 @@
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G505" s="3" t="inlineStr">
@@ -42755,22 +42755,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -44851,12 +44851,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D33" s="24" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">

--- a/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
+++ b/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
@@ -19661,38 +19661,30 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H289" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I289" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H289" s="5" t="n">
+        <v>20300000</v>
+      </c>
+      <c r="I289" s="5" t="n">
+        <v>33170</v>
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K289" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L289" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K289" s="5" t="n">
+        <v>20300000</v>
+      </c>
+      <c r="L289" s="5" t="n">
+        <v>33170</v>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
@@ -19701,7 +19693,7 @@
       </c>
       <c r="N289" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -22805,38 +22797,30 @@
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H337" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I337" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H337" s="5" t="n">
+        <v>53450000</v>
+      </c>
+      <c r="I337" s="5" t="n">
+        <v>39158</v>
       </c>
       <c r="J337" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K337" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L337" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K337" s="5" t="n">
+        <v>53450000</v>
+      </c>
+      <c r="L337" s="5" t="n">
+        <v>39158</v>
       </c>
       <c r="M337" s="3" t="inlineStr">
         <is>
@@ -22845,7 +22829,7 @@
       </c>
       <c r="N337" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27403,7 @@
       </c>
       <c r="F406" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G406" s="3" t="inlineStr">
@@ -27429,12 +27413,12 @@
       </c>
       <c r="H406" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I406" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J406" s="3" t="inlineStr">
@@ -27444,12 +27428,12 @@
       </c>
       <c r="K406" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L406" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M406" s="3" t="inlineStr">
@@ -27459,7 +27443,7 @@
       </c>
       <c r="N406" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -39267,12 +39251,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>143</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -42361,12 +42345,12 @@
 (25年-12月-16日)</t>
         </is>
       </c>
-      <c r="F39" s="22" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
         <is>
           <t>A5 | 612呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$2030万
+$33,170/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr"/>
@@ -42755,27 +42739,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>97</t>
         </is>
       </c>
     </row>
@@ -43206,12 +43190,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="O11" s="22" t="inlineStr">
+      <c r="O11" s="23" t="inlineStr">
         <is>
           <t>D | 1365呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$5345万
+$39,158/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="P11" s="20" t="inlineStr"/>
@@ -43893,12 +43877,12 @@
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr"/>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">

--- a/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
+++ b/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -6889,31 +6889,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H95" s="5" t="n">
-        <v>16513500</v>
-      </c>
-      <c r="I95" s="5" t="n">
-        <v>34260</v>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="K95" s="5" t="n">
-        <v>16018095</v>
-      </c>
-      <c r="L95" s="5" t="n">
-        <v>33233</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>360日付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9233,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -12525,38 +12533,30 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H181" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I181" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>22296000</v>
+      </c>
+      <c r="I181" s="5" t="n">
+        <v>36431</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K181" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L181" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K181" s="5" t="n">
+        <v>22296000</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>36431</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="N181" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23263,38 +23263,30 @@
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H344" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I344" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H344" s="5" t="n">
+        <v>93058000</v>
+      </c>
+      <c r="I344" s="5" t="n">
+        <v>46881</v>
       </c>
       <c r="J344" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K344" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L344" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K344" s="5" t="n">
+        <v>93058000</v>
+      </c>
+      <c r="L344" s="5" t="n">
+        <v>46881</v>
       </c>
       <c r="M344" s="3" t="inlineStr">
         <is>
@@ -23303,7 +23295,7 @@
       </c>
       <c r="N344" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -27403,7 +27395,7 @@
       </c>
       <c r="F406" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G406" s="3" t="inlineStr">
@@ -32573,7 +32565,7 @@
       </c>
       <c r="F485" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G485" s="3" t="inlineStr">
@@ -33885,38 +33877,30 @@
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H505" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I505" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H505" s="5" t="n">
+        <v>15814800</v>
+      </c>
+      <c r="I505" s="5" t="n">
+        <v>35459</v>
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K505" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L505" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K505" s="5" t="n">
+        <v>15814800</v>
+      </c>
+      <c r="L505" s="5" t="n">
+        <v>35459</v>
       </c>
       <c r="M505" s="3" t="inlineStr">
         <is>
@@ -33925,7 +33909,7 @@
       </c>
       <c r="N505" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -35194,7 +35178,7 @@
       </c>
       <c r="G525" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H525" s="5" t="n">
@@ -39246,12 +39230,12 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>144</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40554,12 +40538,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I23" s="25" t="inlineStr">
+      <c r="I23" s="24" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
-$1651万
-$34,260/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="J23" s="25" t="inlineStr">
@@ -40893,12 +40877,12 @@
 (25年-12月-03日)</t>
         </is>
       </c>
-      <c r="I26" s="24" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -41328,12 +41312,12 @@
 (25年-12月-16日)</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>A5 | 612呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$2230万
+$36,431/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr"/>
@@ -42739,22 +42723,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -43209,12 +43193,12 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 1985呎 (4+房)
-招标单位
--
-(在售)</t>
+$9306万
+$46,881/呎
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr"/>
@@ -43877,12 +43861,12 @@
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr"/>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -44645,12 +44629,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D31" s="24" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -44835,12 +44819,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1581万
+$35,459/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -45030,7 +45014,7 @@
           <t>A2 | 446呎 (2房)
 $1552万
 $34,807/呎
-(26年-09月-15日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">

--- a/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
+++ b/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
@@ -11964,7 +11964,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -23869,7 +23869,7 @@
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G353" s="3" t="inlineStr">
@@ -23879,12 +23879,12 @@
       </c>
       <c r="H353" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I353" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J353" s="3" t="inlineStr">
@@ -23894,12 +23894,12 @@
       </c>
       <c r="K353" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L353" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M353" s="3" t="inlineStr">
@@ -23909,7 +23909,7 @@
       </c>
       <c r="N353" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -39042,7 +39042,7 @@
       </c>
       <c r="G585" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H585" s="5" t="n">
@@ -41180,7 +41180,7 @@
           <t>A1 | 908呎 (4+房)
 $3702万
 $40,773/呎
-(26年-09月-08日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -42738,12 +42738,12 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
     </row>
@@ -43386,12 +43386,12 @@
 (25年-11月-18日)</t>
         </is>
       </c>
-      <c r="O15" s="21" t="inlineStr">
+      <c r="O15" s="22" t="inlineStr">
         <is>
           <t>D | 1365呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(暂停销售)</t>
         </is>
       </c>
       <c r="P15" s="20" t="inlineStr"/>
@@ -45584,7 +45584,7 @@
           <t>A2 | 446呎 (2房)
 $1446万
 $32,417/呎
-(26年-09月-22日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">

--- a/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
+++ b/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
@@ -2619,7 +2619,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -9233,38 +9233,30 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H131" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I131" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>29046</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K131" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L131" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K131" s="5" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>29046</v>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
@@ -9273,7 +9265,7 @@
       </c>
       <c r="N131" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -17433,7 +17425,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -22793,7 +22785,7 @@
         </is>
       </c>
       <c r="E337" s="4" t="n">
-        <v>1365</v>
+        <v>1293</v>
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
@@ -22802,14 +22794,14 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
         <v>53450000</v>
       </c>
       <c r="I337" s="5" t="n">
-        <v>39158</v>
+        <v>41338</v>
       </c>
       <c r="J337" s="3" t="inlineStr">
         <is>
@@ -22820,7 +22812,7 @@
         <v>53450000</v>
       </c>
       <c r="L337" s="5" t="n">
-        <v>39158</v>
+        <v>41338</v>
       </c>
       <c r="M337" s="3" t="inlineStr">
         <is>
@@ -32565,38 +32557,30 @@
       </c>
       <c r="F485" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H485" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I485" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H485" s="5" t="n">
+        <v>16150000</v>
+      </c>
+      <c r="I485" s="5" t="n">
+        <v>36211</v>
       </c>
       <c r="J485" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K485" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L485" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K485" s="5" t="n">
+        <v>16150000</v>
+      </c>
+      <c r="L485" s="5" t="n">
+        <v>36211</v>
       </c>
       <c r="M485" s="3" t="inlineStr">
         <is>
@@ -32605,7 +32589,7 @@
       </c>
       <c r="N485" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39225,7 +39209,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39235,12 +39219,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>145</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -39785,12 +39769,12 @@
       <c r="M12" s="20" t="inlineStr"/>
       <c r="N12" s="20" t="inlineStr"/>
       <c r="O12" s="20" t="inlineStr"/>
-      <c r="P12" s="24" t="inlineStr">
+      <c r="P12" s="22" t="inlineStr">
         <is>
           <t>C | 1511呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="Q12" s="20" t="inlineStr"/>
@@ -40877,12 +40861,12 @@
 (25年-12月-03日)</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I26" s="23" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1400万
+$29,046/呎
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -41974,12 +41958,12 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>A2 | 450呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -42733,12 +42717,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -43176,10 +43160,10 @@
       </c>
       <c r="O11" s="23" t="inlineStr">
         <is>
-          <t>D | 1365呎 (4+房)
+          <t>D | 1293呎 (4+房)
 $5345万
-$39,158/呎
-(26年-09月-29日)</t>
+$41,338/呎
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="P11" s="20" t="inlineStr"/>
@@ -44629,12 +44613,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1615万
+$36,211/呎
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">

--- a/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
+++ b/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
@@ -12530,14 +12530,14 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
         <v>22296000</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>36431</v>
+        <v>36491</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>22296000</v>
       </c>
       <c r="L181" s="5" t="n">
-        <v>36431</v>
+        <v>36491</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -13443,12 +13443,12 @@
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I195" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J195" s="3" t="inlineStr">
@@ -13458,12 +13458,12 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L195" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M195" s="3" t="inlineStr">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="N195" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19777,38 +19777,30 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H291" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I291" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H291" s="5" t="n">
+        <v>15173900</v>
+      </c>
+      <c r="I291" s="5" t="n">
+        <v>33720</v>
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K291" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L291" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K291" s="5" t="n">
+        <v>15173900</v>
+      </c>
+      <c r="L291" s="5" t="n">
+        <v>33720</v>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
@@ -19817,7 +19809,7 @@
       </c>
       <c r="N291" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -21981,7 +21973,7 @@
       </c>
       <c r="F325" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G325" s="3" t="inlineStr">
@@ -23251,7 +23243,7 @@
         </is>
       </c>
       <c r="E344" s="4" t="n">
-        <v>1985</v>
+        <v>1915</v>
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
@@ -23260,14 +23252,14 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
         <v>93058000</v>
       </c>
       <c r="I344" s="5" t="n">
-        <v>46881</v>
+        <v>48594</v>
       </c>
       <c r="J344" s="3" t="inlineStr">
         <is>
@@ -23278,7 +23270,7 @@
         <v>93058000</v>
       </c>
       <c r="L344" s="5" t="n">
-        <v>46881</v>
+        <v>48594</v>
       </c>
       <c r="M344" s="3" t="inlineStr">
         <is>
@@ -23861,38 +23853,30 @@
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H353" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I353" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H353" s="5" t="n">
+        <v>54010420</v>
+      </c>
+      <c r="I353" s="5" t="n">
+        <v>39568</v>
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K353" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L353" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K353" s="5" t="n">
+        <v>54010420</v>
+      </c>
+      <c r="L353" s="5" t="n">
+        <v>39568</v>
       </c>
       <c r="M353" s="3" t="inlineStr">
         <is>
@@ -23901,7 +23885,7 @@
       </c>
       <c r="N353" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -27387,38 +27371,30 @@
       </c>
       <c r="F406" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H406" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I406" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H406" s="5" t="n">
+        <v>41436960</v>
+      </c>
+      <c r="I406" s="5" t="n">
+        <v>45635</v>
       </c>
       <c r="J406" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K406" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L406" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K406" s="5" t="n">
+        <v>41436960</v>
+      </c>
+      <c r="L406" s="5" t="n">
+        <v>45635</v>
       </c>
       <c r="M406" s="3" t="inlineStr">
         <is>
@@ -27427,7 +27403,7 @@
       </c>
       <c r="N406" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -33866,7 +33842,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
@@ -39209,7 +39185,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39219,7 +39195,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>146</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40522,12 +40498,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I23" s="24" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="J23" s="25" t="inlineStr">
@@ -41298,10 +41274,10 @@
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>A5 | 612呎 (2房)
+          <t>A5 | 611呎 (2房)
 $2230万
-$36,431/呎
-(26年-10月-06日)</t>
+$36,491/呎
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr"/>
@@ -41393,12 +41369,12 @@
 (26年-08月-27日)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>A2 | 450呎 (2房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E31" s="25" t="inlineStr">
@@ -42297,12 +42273,12 @@
 (26年-08月-31日)</t>
         </is>
       </c>
-      <c r="D39" s="24" t="inlineStr">
+      <c r="D39" s="23" t="inlineStr">
         <is>
           <t>A2 | 450呎 (2房)
-招标单位
--
-(在售)</t>
+$1517万
+$33,720/呎
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
@@ -42707,22 +42683,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -42999,12 +42975,12 @@
 (25年-11月-20日)</t>
         </is>
       </c>
-      <c r="O8" s="22" t="inlineStr">
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t>D | 1365呎 (4+房)
 招标单位
 -
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="P8" s="20" t="inlineStr"/>
@@ -43179,10 +43155,10 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>A | 1985呎 (4+房)
+          <t>A | 1915呎 (4+房)
 $9306万
-$46,881/呎
-(26年-10月-08日)</t>
+$48,594/呎
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr"/>
@@ -43370,12 +43346,12 @@
 (25年-11月-18日)</t>
         </is>
       </c>
-      <c r="O15" s="22" t="inlineStr">
+      <c r="O15" s="23" t="inlineStr">
         <is>
           <t>D | 1365呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$5401万
+$39,568/呎
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="P15" s="20" t="inlineStr"/>
@@ -43845,12 +43821,12 @@
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr"/>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$4144万
+$45,635/呎
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -44808,7 +44784,7 @@
           <t>A2 | 446呎 (2房)
 $1581万
 $35,459/呎
-(26年-10月-06日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">

--- a/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
+++ b/九龙-启德-天玺．天第2期/天玺．天第2期_销控明细表.xlsx
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>22296000</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>36491</v>
+        <v>36431</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>22296000</v>
       </c>
       <c r="L181" s="5" t="n">
-        <v>36491</v>
+        <v>36431</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -17163,12 +17163,12 @@
       </c>
       <c r="H251" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I251" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J251" s="3" t="inlineStr">
@@ -17178,12 +17178,12 @@
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L251" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
@@ -17193,7 +17193,7 @@
       </c>
       <c r="N251" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -20545,31 +20545,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H303" s="5" t="n">
-        <v>13802100</v>
-      </c>
-      <c r="I303" s="5" t="n">
-        <v>30671</v>
+      <c r="H303" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I303" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="K303" s="5" t="n">
-        <v>12421890</v>
-      </c>
-      <c r="L303" s="5" t="n">
-        <v>27604</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K303" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L303" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M303" s="3" t="inlineStr">
         <is>
-          <t>360日付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N303" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -22777,7 +22785,7 @@
         </is>
       </c>
       <c r="E337" s="4" t="n">
-        <v>1293</v>
+        <v>1365</v>
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
@@ -22793,7 +22801,7 @@
         <v>53450000</v>
       </c>
       <c r="I337" s="5" t="n">
-        <v>41338</v>
+        <v>39158</v>
       </c>
       <c r="J337" s="3" t="inlineStr">
         <is>
@@ -22804,7 +22812,7 @@
         <v>53450000</v>
       </c>
       <c r="L337" s="5" t="n">
-        <v>41338</v>
+        <v>39158</v>
       </c>
       <c r="M337" s="3" t="inlineStr">
         <is>
@@ -23243,7 +23251,7 @@
         </is>
       </c>
       <c r="E344" s="4" t="n">
-        <v>1915</v>
+        <v>1985</v>
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
@@ -23259,7 +23267,7 @@
         <v>93058000</v>
       </c>
       <c r="I344" s="5" t="n">
-        <v>48594</v>
+        <v>46881</v>
       </c>
       <c r="J344" s="3" t="inlineStr">
         <is>
@@ -23270,7 +23278,7 @@
         <v>93058000</v>
       </c>
       <c r="L344" s="5" t="n">
-        <v>48594</v>
+        <v>46881</v>
       </c>
       <c r="M344" s="3" t="inlineStr">
         <is>
@@ -39185,7 +39193,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39200,12 +39208,12 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>123</t>
         </is>
       </c>
     </row>
@@ -41274,9 +41282,9 @@
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>A5 | 611呎 (2房)
+          <t>A5 | 612呎 (2房)
 $2230万
-$36,491/呎
+$36,431/呎
 (26年-10月-27日)</t>
         </is>
       </c>
@@ -41967,12 +41975,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I36" s="21" t="inlineStr">
+      <c r="I36" s="24" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="J36" s="25" t="inlineStr">
@@ -42294,7 +42302,7 @@
           <t>A5 | 612呎 (2房)
 $2030万
 $33,170/呎
-(26年-09月-29日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr"/>
@@ -42386,12 +42394,12 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="D40" s="22" t="inlineStr">
+      <c r="D40" s="24" t="inlineStr">
         <is>
           <t>A2 | 450呎 (2房)
-$1380万
-$30,671/呎
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E40" s="23" t="inlineStr">
@@ -43136,9 +43144,9 @@
       </c>
       <c r="O11" s="23" t="inlineStr">
         <is>
-          <t>D | 1293呎 (4+房)
+          <t>D | 1365呎 (4+房)
 $5345万
-$41,338/呎
+$39,158/呎
 (26年-10月-15日)</t>
         </is>
       </c>
@@ -43155,9 +43163,9 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>A | 1915呎 (4+房)
+          <t>A | 1985呎 (4+房)
 $9306万
-$48,594/呎
+$46,881/呎
 (26年-10月-27日)</t>
         </is>
       </c>
